--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1485,6 +1485,67 @@
       </c>
       <c r="M17" s="2" t="n">
         <v>16109.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1109692-241-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>62.000.760-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>22457.57</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1608,71 @@
         <v>22457.57</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1208110-42-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>33575.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
